--- a/paper_info_0021.xlsx
+++ b/paper_info_0021.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>See source_artifacts/Paper_CorporateBoards/</t>
+          <t>Hu, S., et al.</t>
         </is>
       </c>
     </row>
